--- a/artfynd/A 69914-2021 artfynd.xlsx
+++ b/artfynd/A 69914-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69914-2021 artfynd.xlsx
+++ b/artfynd/A 69914-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7084676</v>
+        <v>7084560</v>
       </c>
       <c r="B2" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3624</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525602.7419736071</v>
+        <v>525231</v>
       </c>
       <c r="R2" t="n">
-        <v>7033054.879747273</v>
+        <v>7033284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-10-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>risfattig, gammal barrskog</t>
+          <t>skiktad, gammal,  risfattig barrskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,50 +789,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7084558</v>
+        <v>7084562</v>
       </c>
       <c r="B3" t="n">
-        <v>85254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>249228</v>
+        <v>462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Violettrandad spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius pseudoglaucopus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Jul.Schäff. ex M.M.Moser) Quadr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ammeråns N sida, S om Hannflyberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525235.3159600216</v>
+        <v>525254</v>
       </c>
       <c r="R3" t="n">
-        <v>7033248.091175437</v>
+        <v>7033337</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,33 +860,29 @@
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ej mikroskopierad eller fotad. Osäker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>140-årig barrskog med enbuskar</t>
+          <t>skiktad, gammal, barrskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -903,7 +890,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # barrmatta under gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,15 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7084555</v>
+        <v>7084554</v>
       </c>
       <c r="B4" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525376.1123075063</v>
+        <v>525410</v>
       </c>
       <c r="R4" t="n">
-        <v>7033190.99397555</v>
+        <v>7033215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,21 +980,11 @@
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1024,7 +996,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>140-årig ljus tallskog med enbuskar</t>
+          <t>140-årig barrskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1032,7 +1004,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1057,12 +1029,7 @@
         <v>7084557</v>
       </c>
       <c r="B5" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,14 +1046,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525296.8146732592</v>
+        <v>525297</v>
       </c>
       <c r="R5" t="n">
-        <v>7033239.173817032</v>
+        <v>7033239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,19 +1090,9 @@
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,15 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7084678</v>
+        <v>7084676</v>
       </c>
       <c r="B6" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,14 +1156,10 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1223,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525561.7568422033</v>
+        <v>525603</v>
       </c>
       <c r="R6" t="n">
-        <v>7033077.38980416</v>
+        <v>7033055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,22 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1216,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>risfattig, gammal och grov barrskog med örtinslag</t>
+          <t>risfattig, gammal barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,15 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7084679</v>
+        <v>7084678</v>
       </c>
       <c r="B7" t="n">
-        <v>85254</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,23 +1249,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>249228</v>
+        <v>3624</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1344,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525254.3397011115</v>
+        <v>525562</v>
       </c>
       <c r="R7" t="n">
-        <v>7033337.347720338</v>
+        <v>7033077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,21 +1302,11 @@
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1403,12 +1318,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>skiktad, gammal, barrskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>barrmatta under gran</t>
+          <t>risfattig, gammal och grov barrskog med örtinslag</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1430,39 +1340,30 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7084554</v>
+        <v>7084680</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1470,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525410.0026936067</v>
+        <v>525309</v>
       </c>
       <c r="R8" t="n">
-        <v>7033214.547863564</v>
+        <v>7033298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,21 +1404,11 @@
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1529,15 +1420,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>140-årig barrskog</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
+          <t>skiktad, gammal, barrskog</t>
+        </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>barrmatta under gra</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1559,15 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7084556</v>
+        <v>7084550</v>
       </c>
       <c r="B9" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,34 +1458,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4405</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ammeråns N sida, S om Hannflyberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525306.6784612915</v>
+        <v>525615</v>
       </c>
       <c r="R9" t="n">
-        <v>7033239.251871513</v>
+        <v>7033038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,36 +1515,32 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Är sannolikt felbestämd, troligtvis en art ur calochrous-gruppen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>140-årig barrskog med enbuskar</t>
+          <t>risfattig, gammal barrskog</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1666,7 +1548,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # barrmatta under gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1688,15 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7084560</v>
+        <v>7084555</v>
       </c>
       <c r="B10" t="n">
-        <v>85129</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,21 +1581,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>427</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1728,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525230.9945903197</v>
+        <v>525376</v>
       </c>
       <c r="R10" t="n">
-        <v>7033284.326784485</v>
+        <v>7033191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,21 +1638,11 @@
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1787,7 +1654,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>skiktad, gammal,  risfattig barrskog</t>
+          <t>140-årig ljus tallskog med enbuskar</t>
         </is>
       </c>
       <c r="AN10" t="n">
@@ -1820,12 +1687,7 @@
         <v>7084559</v>
       </c>
       <c r="B11" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525224.4777826935</v>
+        <v>525224</v>
       </c>
       <c r="R11" t="n">
-        <v>7033257.856727036</v>
+        <v>7033258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1890,19 +1752,9 @@
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1946,15 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7084680</v>
+        <v>7084556</v>
       </c>
       <c r="B12" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,21 +1809,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3624</v>
+        <v>4405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1986,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525308.9042956552</v>
+        <v>525307</v>
       </c>
       <c r="R12" t="n">
-        <v>7033297.927894532</v>
+        <v>7033239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,21 +1866,11 @@
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2013-10-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2045,12 +1882,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>skiktad, gammal, barrskog</t>
-        </is>
+          <t>140-årig barrskog med enbuskar</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>barrmatta under gra</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2072,15 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7084562</v>
+        <v>97373546</v>
       </c>
       <c r="B13" t="n">
-        <v>85265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dialog hos validator</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,37 +1923,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>462</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettrandad spindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoglaucopus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Jul.Schäff. ex M.M.Moser) Quadr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ammeråns N sida, S om Hannflyberget, Jmt</t>
+          <t>Ammerån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525254.3397011115</v>
+        <v>525303</v>
       </c>
       <c r="R13" t="n">
-        <v>7033337.347720338</v>
+        <v>7033299</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2145,119 +1981,78 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ej mikroskopierad eller fotad. Osäker.</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>skiktad, gammal, barrskog</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>1 substratenheter # barrmatta under gran</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97373546</v>
+        <v>7084558</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87323</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>249228</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ammerån, Jmt</t>
+          <t>Ammeråns N sida, S om Hannflyberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525302.6168249621</v>
+        <v>525235</v>
       </c>
       <c r="R14" t="n">
-        <v>7033299.221440921</v>
+        <v>7033248</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2284,22 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2308,22 +2093,149 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>140-årig barrskog med enbuskar</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7084679</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ammeråns N sida, S om Hannflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>525254</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7033337</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2013-10-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2013-10-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>skiktad, gammal, barrskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>barrmatta under gran</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69914-2021 artfynd.xlsx
+++ b/artfynd/A 69914-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084560</t>
         </is>
       </c>
     </row>
@@ -909,6 +919,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084562</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084554</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084557</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084676</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084678</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084680</t>
         </is>
       </c>
     </row>
@@ -1567,6 +1607,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084555</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1795,6 +1845,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084559</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084556</t>
         </is>
       </c>
     </row>
@@ -2011,6 +2071,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97373546</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2125,6 +2190,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084558</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2236,8 +2306,29 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7084679</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>